--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/17.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/17.xlsx
@@ -426,13 +426,13 @@
         <v>-19.69811225773058</v>
       </c>
       <c r="E2">
-        <v>-18.35319625937636</v>
+        <v>-23.7106255480468</v>
       </c>
       <c r="F2">
-        <v>-0.9167104484533722</v>
+        <v>-3.393260591785387</v>
       </c>
       <c r="G2">
-        <v>-11.90434289795665</v>
+        <v>-16.25111654966934</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.05249837644792</v>
       </c>
       <c r="E3">
-        <v>-19.19359952266784</v>
+        <v>-24.83192099708606</v>
       </c>
       <c r="F3">
-        <v>-1.121092709378692</v>
+        <v>-3.388618420860098</v>
       </c>
       <c r="G3">
-        <v>-11.78829921628533</v>
+        <v>-14.9977194449555</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.32435627832468</v>
       </c>
       <c r="E4">
-        <v>-19.49210747230545</v>
+        <v>-25.42966145220252</v>
       </c>
       <c r="F4">
-        <v>-1.056999438321885</v>
+        <v>-2.981414543196335</v>
       </c>
       <c r="G4">
-        <v>-11.56427381431424</v>
+        <v>-16.19462047685882</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.59372576867018</v>
       </c>
       <c r="E5">
-        <v>-20.22305751883154</v>
+        <v>-24.94277351231982</v>
       </c>
       <c r="F5">
-        <v>-0.9713296815243604</v>
+        <v>-2.985367512442493</v>
       </c>
       <c r="G5">
-        <v>-11.10135251426466</v>
+        <v>-15.58529763326994</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.85869990665509</v>
       </c>
       <c r="E6">
-        <v>-20.96006213510588</v>
+        <v>-26.14399199912046</v>
       </c>
       <c r="F6">
-        <v>-0.9709320651710167</v>
+        <v>-3.076963409639646</v>
       </c>
       <c r="G6">
-        <v>-11.05766633042222</v>
+        <v>-15.36687491711161</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.15583399165405</v>
       </c>
       <c r="E7">
-        <v>-21.06771754769023</v>
+        <v>-26.98398317127724</v>
       </c>
       <c r="F7">
-        <v>-0.9522532086052906</v>
+        <v>-3.225034082890058</v>
       </c>
       <c r="G7">
-        <v>-10.50582064489013</v>
+        <v>-14.60113952300555</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.50722974584016</v>
       </c>
       <c r="E8">
-        <v>-20.69453959014014</v>
+        <v>-26.3122791501935</v>
       </c>
       <c r="F8">
-        <v>-0.7407983467948692</v>
+        <v>-3.082748727580798</v>
       </c>
       <c r="G8">
-        <v>-10.62464024000074</v>
+        <v>-14.81935224098408</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.91388185728335</v>
       </c>
       <c r="E9">
-        <v>-21.69285527055309</v>
+        <v>-26.88682476144267</v>
       </c>
       <c r="F9">
-        <v>-0.8114862507453623</v>
+        <v>-2.893136257447394</v>
       </c>
       <c r="G9">
-        <v>-10.60497587919498</v>
+        <v>-15.42218975016072</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.38062594849293</v>
       </c>
       <c r="E10">
-        <v>-22.66591112295126</v>
+        <v>-28.03365174693717</v>
       </c>
       <c r="F10">
-        <v>-0.4740549310519976</v>
+        <v>-2.935730909299345</v>
       </c>
       <c r="G10">
-        <v>-9.820127369505165</v>
+        <v>-14.66950541480736</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.92542249813441</v>
       </c>
       <c r="E11">
-        <v>-23.23655771807983</v>
+        <v>-28.00522198711702</v>
       </c>
       <c r="F11">
-        <v>-0.436930817528135</v>
+        <v>-2.480648224121172</v>
       </c>
       <c r="G11">
-        <v>-9.718019035796805</v>
+        <v>-14.53562009090656</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.53272350055257</v>
       </c>
       <c r="E12">
-        <v>-23.33128886584628</v>
+        <v>-29.17428377998918</v>
       </c>
       <c r="F12">
-        <v>-0.2388822537646208</v>
+        <v>-3.004926923557396</v>
       </c>
       <c r="G12">
-        <v>-9.200012588207269</v>
+        <v>-14.47121955535934</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.19570454656903</v>
       </c>
       <c r="E13">
-        <v>-23.98569411622072</v>
+        <v>-28.95494714142767</v>
       </c>
       <c r="F13">
-        <v>-0.2254693287784912</v>
+        <v>-2.367077396462554</v>
       </c>
       <c r="G13">
-        <v>-8.99418812222642</v>
+        <v>-13.68397247270956</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.9290757510541</v>
       </c>
       <c r="E14">
-        <v>-25.1302659216594</v>
+        <v>-29.7700498204383</v>
       </c>
       <c r="F14">
-        <v>0.06033399253539424</v>
+        <v>-2.456365462075507</v>
       </c>
       <c r="G14">
-        <v>-8.524760159824462</v>
+        <v>-13.48531419461454</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.71602231534338</v>
       </c>
       <c r="E15">
-        <v>-25.42725230403044</v>
+        <v>-30.43897335848132</v>
       </c>
       <c r="F15">
-        <v>0.2056080974339548</v>
+        <v>-2.12317952532149</v>
       </c>
       <c r="G15">
-        <v>-7.902302586333121</v>
+        <v>-12.98108559635311</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.5453788756127</v>
       </c>
       <c r="E16">
-        <v>-25.72265372049879</v>
+        <v>-31.58444180177352</v>
       </c>
       <c r="F16">
-        <v>0.2608775989161405</v>
+        <v>-1.68568308010475</v>
       </c>
       <c r="G16">
-        <v>-7.590527476197804</v>
+        <v>-12.91498210681654</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.42394116203503</v>
       </c>
       <c r="E17">
-        <v>-26.7747903144929</v>
+        <v>-31.51278322907615</v>
       </c>
       <c r="F17">
-        <v>0.6934245489011528</v>
+        <v>-1.591790948467038</v>
       </c>
       <c r="G17">
-        <v>-7.430653236935419</v>
+        <v>-12.26410915462041</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.33373889757655</v>
       </c>
       <c r="E18">
-        <v>-27.69002208228713</v>
+        <v>-33.30482039847251</v>
       </c>
       <c r="F18">
-        <v>0.9319603978438956</v>
+        <v>-1.70451104280298</v>
       </c>
       <c r="G18">
-        <v>-7.106232298910001</v>
+        <v>-12.64425179716832</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-12.25604624815229</v>
       </c>
       <c r="E19">
-        <v>-28.0155423793805</v>
+        <v>-33.54682884215342</v>
       </c>
       <c r="F19">
-        <v>1.023271336654485</v>
+        <v>-1.750195505067373</v>
       </c>
       <c r="G19">
-        <v>-6.879168485774867</v>
+        <v>-12.65183798141375</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.19092539535212</v>
       </c>
       <c r="E20">
-        <v>-28.41715915369876</v>
+        <v>-33.5594451707388</v>
       </c>
       <c r="F20">
-        <v>1.116815553983022</v>
+        <v>-1.126887139361274</v>
       </c>
       <c r="G20">
-        <v>-6.870784964690486</v>
+        <v>-11.64659966324071</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.12532334004158</v>
       </c>
       <c r="E21">
-        <v>-29.31683108480263</v>
+        <v>-34.97941612295395</v>
       </c>
       <c r="F21">
-        <v>1.618898977228636</v>
+        <v>-1.017715770978924</v>
       </c>
       <c r="G21">
-        <v>-6.692417760719072</v>
+        <v>-11.12987617328092</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.04446307885782</v>
       </c>
       <c r="E22">
-        <v>-30.29640341129783</v>
+        <v>-33.95715160775143</v>
       </c>
       <c r="F22">
-        <v>1.699189316112381</v>
+        <v>-1.223264373207385</v>
       </c>
       <c r="G22">
-        <v>-7.025750496499941</v>
+        <v>-11.51779202970315</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.95486510320137</v>
       </c>
       <c r="E23">
-        <v>-30.06100427543111</v>
+        <v>-35.36737049119107</v>
       </c>
       <c r="F23">
-        <v>1.704442822180935</v>
+        <v>-0.1549553819825861</v>
       </c>
       <c r="G23">
-        <v>-6.814377484862073</v>
+        <v>-11.49216568932389</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.85834057467253</v>
       </c>
       <c r="E24">
-        <v>-30.7399991396672</v>
+        <v>-35.26884674644319</v>
       </c>
       <c r="F24">
-        <v>2.010670370178246</v>
+        <v>-0.7866965278491842</v>
       </c>
       <c r="G24">
-        <v>-6.459126189064111</v>
+        <v>-11.06614172571026</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.74907760626764</v>
       </c>
       <c r="E25">
-        <v>-31.16705008824954</v>
+        <v>-36.0899021045369</v>
       </c>
       <c r="F25">
-        <v>2.306831597496736</v>
+        <v>-0.514563753783699</v>
       </c>
       <c r="G25">
-        <v>-6.662808017366642</v>
+        <v>-11.62429720030116</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.6384241856384</v>
       </c>
       <c r="E26">
-        <v>-31.18733991604091</v>
+        <v>-35.69539050593667</v>
       </c>
       <c r="F26">
-        <v>2.11211721252949</v>
+        <v>-0.2138539610564365</v>
       </c>
       <c r="G26">
-        <v>-6.27436060305178</v>
+        <v>-11.27176603717598</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.53538788030539</v>
       </c>
       <c r="E27">
-        <v>-30.71468044149032</v>
+        <v>-36.13216861668749</v>
       </c>
       <c r="F27">
-        <v>2.254776989904815</v>
+        <v>-0.1998139619463877</v>
       </c>
       <c r="G27">
-        <v>-6.545464971957781</v>
+        <v>-11.11836892927194</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.43326659315269</v>
       </c>
       <c r="E28">
-        <v>-31.28101819360058</v>
+        <v>-36.78091780302635</v>
       </c>
       <c r="F28">
-        <v>2.149279430953881</v>
+        <v>-0.4619085798247485</v>
       </c>
       <c r="G28">
-        <v>-6.682869405981087</v>
+        <v>-11.44229440284188</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.33707628062447</v>
       </c>
       <c r="E29">
-        <v>-31.70047941974607</v>
+        <v>-36.70146119808776</v>
       </c>
       <c r="F29">
-        <v>1.970032322131707</v>
+        <v>-0.6096826975449579</v>
       </c>
       <c r="G29">
-        <v>-6.970481600552654</v>
+        <v>-12.07846092000859</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.25453104089737</v>
       </c>
       <c r="E30">
-        <v>-31.17000491753955</v>
+        <v>-36.76060080439093</v>
       </c>
       <c r="F30">
-        <v>2.14240232477584</v>
+        <v>-0.4932150690787502</v>
       </c>
       <c r="G30">
-        <v>-6.800238701162425</v>
+        <v>-11.73686606834104</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.17381160831964</v>
       </c>
       <c r="E31">
-        <v>-30.78619183878244</v>
+        <v>-36.8126578773461</v>
       </c>
       <c r="F31">
-        <v>1.982133113151803</v>
+        <v>-0.3148435446013355</v>
       </c>
       <c r="G31">
-        <v>-7.00755612295282</v>
+        <v>-12.30818252260687</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.09133971185353</v>
       </c>
       <c r="E32">
-        <v>-30.55528947760534</v>
+        <v>-35.32280577848159</v>
       </c>
       <c r="F32">
-        <v>2.048632791513741</v>
+        <v>-0.2521800356817612</v>
       </c>
       <c r="G32">
-        <v>-6.685684694079091</v>
+        <v>-11.60415706236929</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.01299143508241</v>
       </c>
       <c r="E33">
-        <v>-30.65070895342096</v>
+        <v>-35.98521057819057</v>
       </c>
       <c r="F33">
-        <v>2.043062849097317</v>
+        <v>-0.6912437520245972</v>
       </c>
       <c r="G33">
-        <v>-7.18725222165581</v>
+        <v>-11.92258320860561</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.92336552358467</v>
       </c>
       <c r="E34">
-        <v>-30.28976466840259</v>
+        <v>-33.87789425566918</v>
       </c>
       <c r="F34">
-        <v>1.823045153444157</v>
+        <v>-0.5665288976961176</v>
       </c>
       <c r="G34">
-        <v>-7.207503921120703</v>
+        <v>-11.95027343734576</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.81441364571147</v>
       </c>
       <c r="E35">
-        <v>-30.54518645209422</v>
+        <v>-34.71862130485221</v>
       </c>
       <c r="F35">
-        <v>1.84451312305511</v>
+        <v>-1.014476026066575</v>
       </c>
       <c r="G35">
-        <v>-7.086735280403781</v>
+        <v>-12.45108300274225</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.69176841155971</v>
       </c>
       <c r="E36">
-        <v>-30.25901632989051</v>
+        <v>-34.52350747375773</v>
       </c>
       <c r="F36">
-        <v>2.008480166765243</v>
+        <v>-0.7622572043643904</v>
       </c>
       <c r="G36">
-        <v>-7.432044474876624</v>
+        <v>-11.66759948122116</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.54524417681742</v>
       </c>
       <c r="E37">
-        <v>-28.75732906420694</v>
+        <v>-34.25707923399045</v>
       </c>
       <c r="F37">
-        <v>1.886158465863452</v>
+        <v>-0.320642116420932</v>
       </c>
       <c r="G37">
-        <v>-6.900913141049307</v>
+        <v>-12.14569314976161</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.36926339733166</v>
       </c>
       <c r="E38">
-        <v>-28.65930571583691</v>
+        <v>-34.46650530718618</v>
       </c>
       <c r="F38">
-        <v>2.095694000401587</v>
+        <v>-0.9068106296225154</v>
       </c>
       <c r="G38">
-        <v>-6.773057061763985</v>
+        <v>-11.94335990352001</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.17481379390669</v>
       </c>
       <c r="E39">
-        <v>-28.43567608391612</v>
+        <v>-33.26940093902152</v>
       </c>
       <c r="F39">
-        <v>1.952479216866386</v>
+        <v>-0.7548184650872508</v>
       </c>
       <c r="G39">
-        <v>-6.881494871860514</v>
+        <v>-11.73121908603723</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.962528701248001</v>
       </c>
       <c r="E40">
-        <v>-28.27558999927097</v>
+        <v>-33.44244298780261</v>
       </c>
       <c r="F40">
-        <v>1.862607980601862</v>
+        <v>-0.4833989153555761</v>
       </c>
       <c r="G40">
-        <v>-7.553705607857715</v>
+        <v>-12.2630821322723</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.732523009201794</v>
       </c>
       <c r="E41">
-        <v>-27.98612994070068</v>
+        <v>-31.72392106544677</v>
       </c>
       <c r="F41">
-        <v>1.903277506609706</v>
+        <v>-0.8697809499825718</v>
       </c>
       <c r="G41">
-        <v>-6.959827474149137</v>
+        <v>-12.69848054588126</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.5001649817619</v>
       </c>
       <c r="E42">
-        <v>-27.63591587484348</v>
+        <v>-32.61801618081019</v>
       </c>
       <c r="F42">
-        <v>1.884546462897604</v>
+        <v>-0.6868260686654675</v>
       </c>
       <c r="G42">
-        <v>-7.21987084517825</v>
+        <v>-12.1991901860668</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.272840028270029</v>
       </c>
       <c r="E43">
-        <v>-26.52856812574785</v>
+        <v>-32.40597944234905</v>
       </c>
       <c r="F43">
-        <v>1.749774399931735</v>
+        <v>-0.6417015827653672</v>
       </c>
       <c r="G43">
-        <v>-6.763377458163623</v>
+        <v>-12.36190596319966</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.051419750542445</v>
       </c>
       <c r="E44">
-        <v>-26.06234361276216</v>
+        <v>-31.96739673470617</v>
       </c>
       <c r="F44">
-        <v>1.943599118308375</v>
+        <v>-0.7711621539444851</v>
       </c>
       <c r="G44">
-        <v>-6.936251897244527</v>
+        <v>-12.38084845526233</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.84989178869848</v>
       </c>
       <c r="E45">
-        <v>-25.65821806384365</v>
+        <v>-31.39636069081295</v>
       </c>
       <c r="F45">
-        <v>1.909125780473471</v>
+        <v>-0.8352612235731108</v>
       </c>
       <c r="G45">
-        <v>-6.707488411341601</v>
+        <v>-11.81643240993601</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.678371795733167</v>
       </c>
       <c r="E46">
-        <v>-25.32064749741587</v>
+        <v>-30.81397855529351</v>
       </c>
       <c r="F46">
-        <v>1.797594393360545</v>
+        <v>-0.7729390020234901</v>
       </c>
       <c r="G46">
-        <v>-6.852915432077751</v>
+        <v>-11.35481703606709</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.535343143448932</v>
       </c>
       <c r="E47">
-        <v>-25.37812741799523</v>
+        <v>-30.89871536092503</v>
       </c>
       <c r="F47">
-        <v>1.833933214586554</v>
+        <v>-0.7111709582663421</v>
       </c>
       <c r="G47">
-        <v>-7.194539814739337</v>
+        <v>-11.84195375122537</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.429908227552193</v>
       </c>
       <c r="E48">
-        <v>-24.5898831183241</v>
+        <v>-30.70229732931634</v>
       </c>
       <c r="F48">
-        <v>1.782746736032767</v>
+        <v>-0.7286188608715081</v>
       </c>
       <c r="G48">
-        <v>-7.095502704410617</v>
+        <v>-11.67157960297276</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.371017096688272</v>
       </c>
       <c r="E49">
-        <v>-23.94994634240417</v>
+        <v>-30.04721507207776</v>
       </c>
       <c r="F49">
-        <v>1.675867460253964</v>
+        <v>-0.675478263614517</v>
       </c>
       <c r="G49">
-        <v>-6.768515851125714</v>
+        <v>-11.485796838277</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.350836207893026</v>
       </c>
       <c r="E50">
-        <v>-23.88725867671599</v>
+        <v>-29.11388752214888</v>
       </c>
       <c r="F50">
-        <v>1.717492922244639</v>
+        <v>-0.9340879398293003</v>
       </c>
       <c r="G50">
-        <v>-6.535280060237264</v>
+        <v>-12.8032204192803</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.37067214993078</v>
       </c>
       <c r="E51">
-        <v>-23.66997796535395</v>
+        <v>-27.86218560711074</v>
       </c>
       <c r="F51">
-        <v>1.802798197384932</v>
+        <v>-0.7965325623900256</v>
       </c>
       <c r="G51">
-        <v>-7.53972760401448</v>
+        <v>-12.30330334614798</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.437161932702884</v>
       </c>
       <c r="E52">
-        <v>-22.41751073820852</v>
+        <v>-29.33208298526046</v>
       </c>
       <c r="F52">
-        <v>1.835114466502946</v>
+        <v>-0.8650418600711559</v>
       </c>
       <c r="G52">
-        <v>-6.893760078049718</v>
+        <v>-12.47547888503672</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.537542318620964</v>
       </c>
       <c r="E53">
-        <v>-22.15196555087273</v>
+        <v>-28.83400971457882</v>
       </c>
       <c r="F53">
-        <v>1.696339732246751</v>
+        <v>-0.9585579129079976</v>
       </c>
       <c r="G53">
-        <v>-7.171909229643846</v>
+        <v>-11.50069030293532</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.668698633330621</v>
       </c>
       <c r="E54">
-        <v>-22.20840845090434</v>
+        <v>-27.87110217243184</v>
       </c>
       <c r="F54">
-        <v>1.880734316109921</v>
+        <v>-1.175562836317176</v>
       </c>
       <c r="G54">
-        <v>-7.654836137541361</v>
+        <v>-11.76213147434876</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.835730525705946</v>
       </c>
       <c r="E55">
-        <v>-21.97719815349472</v>
+        <v>-27.51953409284636</v>
       </c>
       <c r="F55">
-        <v>1.499859267976736</v>
+        <v>-0.8149985285332322</v>
       </c>
       <c r="G55">
-        <v>-7.508805372038274</v>
+        <v>-12.14217239902832</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.023792463977079</v>
       </c>
       <c r="E56">
-        <v>-21.82840608302469</v>
+        <v>-26.58448572279456</v>
       </c>
       <c r="F56">
-        <v>1.498885107911044</v>
+        <v>-0.5200185531311338</v>
       </c>
       <c r="G56">
-        <v>-7.648004634254597</v>
+        <v>-12.16430423844678</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.225317379433603</v>
       </c>
       <c r="E57">
-        <v>-21.11881684839278</v>
+        <v>-27.0546318942709</v>
       </c>
       <c r="F57">
-        <v>1.521855735990674</v>
+        <v>-0.6400688706144494</v>
       </c>
       <c r="G57">
-        <v>-7.976182570965578</v>
+        <v>-12.25099411204731</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.442466983261278</v>
       </c>
       <c r="E58">
-        <v>-20.62598302213802</v>
+        <v>-27.17712711617839</v>
       </c>
       <c r="F58">
-        <v>1.771648269570059</v>
+        <v>-0.5521915146884638</v>
       </c>
       <c r="G58">
-        <v>-8.017329089321015</v>
+        <v>-12.23101147275029</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.662815352679774</v>
       </c>
       <c r="E59">
-        <v>-20.55255834457765</v>
+        <v>-26.39568911294078</v>
       </c>
       <c r="F59">
-        <v>1.627853628852899</v>
+        <v>-0.4185559717992364</v>
       </c>
       <c r="G59">
-        <v>-7.791174174557848</v>
+        <v>-12.52180973345608</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.876448126055916</v>
       </c>
       <c r="E60">
-        <v>-20.20185067505362</v>
+        <v>-25.60063851683612</v>
       </c>
       <c r="F60">
-        <v>1.538091737085544</v>
+        <v>-0.8506614019585564</v>
       </c>
       <c r="G60">
-        <v>-8.59361659424941</v>
+        <v>-12.35528117687114</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.08528231952301</v>
       </c>
       <c r="E61">
-        <v>-20.13570778369759</v>
+        <v>-25.51544886380383</v>
       </c>
       <c r="F61">
-        <v>1.677507627711507</v>
+        <v>-1.043681775587078</v>
       </c>
       <c r="G61">
-        <v>-8.019990160005726</v>
+        <v>-12.35130105511953</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.28072506928648</v>
       </c>
       <c r="E62">
-        <v>-19.62939269032199</v>
+        <v>-25.72687425827394</v>
       </c>
       <c r="F62">
-        <v>1.376333120871274</v>
+        <v>-0.8770581576161655</v>
       </c>
       <c r="G62">
-        <v>-8.505843917534264</v>
+        <v>-13.59324997781248</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.45186134734766</v>
       </c>
       <c r="E63">
-        <v>-19.58754959049111</v>
+        <v>-25.22653222211446</v>
       </c>
       <c r="F63">
-        <v>1.603435014553175</v>
+        <v>-0.8923589319132752</v>
       </c>
       <c r="G63">
-        <v>-8.234385176699844</v>
+        <v>-13.32966288749916</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.60095850853384</v>
       </c>
       <c r="E64">
-        <v>-18.7874542743419</v>
+        <v>-25.02903641369194</v>
       </c>
       <c r="F64">
-        <v>1.698587921377948</v>
+        <v>-0.8291205360161581</v>
       </c>
       <c r="G64">
-        <v>-8.377607216548045</v>
+        <v>-13.27375743456935</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.72431464197765</v>
       </c>
       <c r="E65">
-        <v>-19.22188889979375</v>
+        <v>-24.63224246419184</v>
       </c>
       <c r="F65">
-        <v>1.432241293621018</v>
+        <v>-1.366015270997019</v>
       </c>
       <c r="G65">
-        <v>-8.539699561584614</v>
+        <v>-13.64137565442485</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.81157863948485</v>
       </c>
       <c r="E66">
-        <v>-19.28076359036747</v>
+        <v>-24.00968597151335</v>
       </c>
       <c r="F66">
-        <v>1.490309848557263</v>
+        <v>-1.187159151588966</v>
       </c>
       <c r="G66">
-        <v>-8.900010501027239</v>
+        <v>-14.03356366131748</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.86622534396018</v>
       </c>
       <c r="E67">
-        <v>-18.91420173334259</v>
+        <v>-25.97578636057955</v>
       </c>
       <c r="F67">
-        <v>1.317022014830829</v>
+        <v>-1.407462633996092</v>
       </c>
       <c r="G67">
-        <v>-8.944041213133428</v>
+        <v>-14.24625080218991</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.89158956777079</v>
       </c>
       <c r="E68">
-        <v>-18.48674095786255</v>
+        <v>-25.31635903253061</v>
       </c>
       <c r="F68">
-        <v>1.19553862174067</v>
+        <v>-1.461474673760828</v>
       </c>
       <c r="G68">
-        <v>-9.208825949315937</v>
+        <v>-13.95718666707829</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.87968996343595</v>
       </c>
       <c r="E69">
-        <v>-18.55480392219784</v>
+        <v>-24.39673011647493</v>
       </c>
       <c r="F69">
-        <v>0.993793054258462</v>
+        <v>-1.447046170338866</v>
       </c>
       <c r="G69">
-        <v>-9.334824857198614</v>
+        <v>-13.69364223264525</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.83515457223645</v>
       </c>
       <c r="E70">
-        <v>-17.73993219536161</v>
+        <v>-23.9022615111034</v>
       </c>
       <c r="F70">
-        <v>1.292152768663982</v>
+        <v>-1.618495856798488</v>
       </c>
       <c r="G70">
-        <v>-8.832236869716908</v>
+        <v>-13.40784455359605</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.76793289714676</v>
       </c>
       <c r="E71">
-        <v>-18.3227558570968</v>
+        <v>-23.92055201762038</v>
       </c>
       <c r="F71">
-        <v>1.074999567489703</v>
+        <v>-1.4095956800583</v>
       </c>
       <c r="G71">
-        <v>-9.106609335296115</v>
+        <v>-13.49737596506706</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.67293672208622</v>
       </c>
       <c r="E72">
-        <v>-17.95565964013901</v>
+        <v>-22.9169697219365</v>
       </c>
       <c r="F72">
-        <v>0.8734544649189722</v>
+        <v>-1.809794882963992</v>
       </c>
       <c r="G72">
-        <v>-8.930798202919508</v>
+        <v>-13.56716426641489</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.55479907757537</v>
       </c>
       <c r="E73">
-        <v>-18.69495113578722</v>
+        <v>-24.04613113032708</v>
       </c>
       <c r="F73">
-        <v>0.7982320778055546</v>
+        <v>-1.767546488686412</v>
       </c>
       <c r="G73">
-        <v>-9.082174078342931</v>
+        <v>-13.90142886911864</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.42869531748701</v>
       </c>
       <c r="E74">
-        <v>-18.29752319992606</v>
+        <v>-24.45329528530474</v>
       </c>
       <c r="F74">
-        <v>0.7586145783992655</v>
+        <v>-1.750304849564543</v>
       </c>
       <c r="G74">
-        <v>-8.598672956672514</v>
+        <v>-13.51240724103088</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.29061428905347</v>
       </c>
       <c r="E75">
-        <v>-19.0884302423137</v>
+        <v>-23.89155167007526</v>
       </c>
       <c r="F75">
-        <v>0.6430937738744577</v>
+        <v>-1.687736602896291</v>
       </c>
       <c r="G75">
-        <v>-9.055688057915093</v>
+        <v>-13.68062562671893</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.14370477859115</v>
       </c>
       <c r="E76">
-        <v>-19.06728226869788</v>
+        <v>-24.4693260832919</v>
       </c>
       <c r="F76">
-        <v>0.5970531136268611</v>
+        <v>-2.177586696337361</v>
       </c>
       <c r="G76">
-        <v>-8.577738763123257</v>
+        <v>-13.00091073701528</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.00274740228736</v>
       </c>
       <c r="E77">
-        <v>-18.96849813669456</v>
+        <v>-25.03667594934288</v>
       </c>
       <c r="F77">
-        <v>0.6043560006499415</v>
+        <v>-1.761774424623705</v>
       </c>
       <c r="G77">
-        <v>-8.554048343464066</v>
+        <v>-12.88796452849607</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.865903854755434</v>
       </c>
       <c r="E78">
-        <v>-19.72643788830636</v>
+        <v>-24.96215990954666</v>
       </c>
       <c r="F78">
-        <v>0.4179078939952316</v>
+        <v>-2.052515644025678</v>
       </c>
       <c r="G78">
-        <v>-8.650145479275523</v>
+        <v>-12.679229618992</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.732949451677612</v>
       </c>
       <c r="E79">
-        <v>-19.41796729585187</v>
+        <v>-26.76316119324121</v>
       </c>
       <c r="F79">
-        <v>0.3417287425315807</v>
+        <v>-2.034333807901632</v>
       </c>
       <c r="G79">
-        <v>-8.191653828331194</v>
+        <v>-12.74985791305905</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.615699504225908</v>
       </c>
       <c r="E80">
-        <v>-20.12441376952246</v>
+        <v>-26.67457518470316</v>
       </c>
       <c r="F80">
-        <v>0.3235816978384519</v>
+        <v>-2.552508267946626</v>
       </c>
       <c r="G80">
-        <v>-7.888616611208677</v>
+        <v>-12.78937366429944</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.512859008508174</v>
       </c>
       <c r="E81">
-        <v>-20.95544309161806</v>
+        <v>-26.50219882160119</v>
       </c>
       <c r="F81">
-        <v>0.2814956635718203</v>
+        <v>-2.255565061799893</v>
       </c>
       <c r="G81">
-        <v>-8.129274525264591</v>
+        <v>-12.42803242128715</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.418851618097694</v>
       </c>
       <c r="E82">
-        <v>-21.61650519878377</v>
+        <v>-26.81143019768897</v>
       </c>
       <c r="F82">
-        <v>0.2246796001486077</v>
+        <v>-2.205521730261969</v>
       </c>
       <c r="G82">
-        <v>-7.44471327131764</v>
+        <v>-11.98256393871226</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.339914720481307</v>
       </c>
       <c r="E83">
-        <v>-22.33819904443818</v>
+        <v>-27.21805999273372</v>
       </c>
       <c r="F83">
-        <v>0.219291070193397</v>
+        <v>-2.217416257798767</v>
       </c>
       <c r="G83">
-        <v>-7.326901011225777</v>
+        <v>-11.91122361956681</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.273802703666455</v>
       </c>
       <c r="E84">
-        <v>-22.88539267268102</v>
+        <v>-27.83361093612234</v>
       </c>
       <c r="F84">
-        <v>0.1280778787363378</v>
+        <v>-2.151092193326222</v>
       </c>
       <c r="G84">
-        <v>-7.57618853798303</v>
+        <v>-11.60685750771272</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.21015336175765</v>
       </c>
       <c r="E85">
-        <v>-24.45590368633316</v>
+        <v>-28.67846116088936</v>
       </c>
       <c r="F85">
-        <v>0.256070582877695</v>
+        <v>-2.489160527552339</v>
       </c>
       <c r="G85">
-        <v>-7.103446541806033</v>
+        <v>-11.63855082675539</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.150683597547872</v>
       </c>
       <c r="E86">
-        <v>-24.69110356934354</v>
+        <v>-30.41041000867794</v>
       </c>
       <c r="F86">
-        <v>0.1397412917677548</v>
+        <v>-2.680327014933395</v>
       </c>
       <c r="G86">
-        <v>-6.812654843543363</v>
+        <v>-11.04363910825559</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.094898156290352</v>
       </c>
       <c r="E87">
-        <v>-26.13349952484468</v>
+        <v>-30.57892584768837</v>
       </c>
       <c r="F87">
-        <v>0.2580835156664978</v>
+        <v>-2.216354290788378</v>
       </c>
       <c r="G87">
-        <v>-6.602735413056329</v>
+        <v>-12.11595871998992</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.031845125072564</v>
       </c>
       <c r="E88">
-        <v>-27.22946721875904</v>
+        <v>-31.5515424381078</v>
       </c>
       <c r="F88">
-        <v>-0.256953088656692</v>
+        <v>-2.377378973483768</v>
       </c>
       <c r="G88">
-        <v>-6.824322867408749</v>
+        <v>-12.63373876329186</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.961903219490932</v>
       </c>
       <c r="E89">
-        <v>-28.72290360480063</v>
+        <v>-33.39522232508764</v>
       </c>
       <c r="F89">
-        <v>0.05878411712475636</v>
+        <v>-2.966998465285414</v>
       </c>
       <c r="G89">
-        <v>-6.868888418629127</v>
+        <v>-10.72076362558467</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.889266224558279</v>
       </c>
       <c r="E90">
-        <v>-30.31225307032468</v>
+        <v>-34.32862006636363</v>
       </c>
       <c r="F90">
-        <v>-0.07350367200011629</v>
+        <v>-2.651376402572955</v>
       </c>
       <c r="G90">
-        <v>-6.564784804499791</v>
+        <v>-11.26407485384065</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.805264001596555</v>
       </c>
       <c r="E91">
-        <v>-31.65673888930598</v>
+        <v>-35.80782345859911</v>
       </c>
       <c r="F91">
-        <v>-0.1828224897801642</v>
+        <v>-2.859470577830219</v>
       </c>
       <c r="G91">
-        <v>-6.382115919063944</v>
+        <v>-10.76431199812162</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.711199557372737</v>
       </c>
       <c r="E92">
-        <v>-32.99802307716386</v>
+        <v>-37.47500607113</v>
       </c>
       <c r="F92">
-        <v>-0.6831961627064</v>
+        <v>-3.126582617067337</v>
       </c>
       <c r="G92">
-        <v>-6.202045761103178</v>
+        <v>-11.0408631948163</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.617041472572158</v>
       </c>
       <c r="E93">
-        <v>-34.73874131486829</v>
+        <v>-38.5478604337092</v>
       </c>
       <c r="F93">
-        <v>-0.4024632782650504</v>
+        <v>-2.994014839760318</v>
       </c>
       <c r="G93">
-        <v>-6.455615281995506</v>
+        <v>-11.76326677700833</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.516856104170619</v>
       </c>
       <c r="E94">
-        <v>-36.63602022020292</v>
+        <v>-39.91002088674244</v>
       </c>
       <c r="F94">
-        <v>-0.6385645554109655</v>
+        <v>-3.311909114258656</v>
       </c>
       <c r="G94">
-        <v>-6.950466149040042</v>
+        <v>-11.65431381512697</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.412462844575535</v>
       </c>
       <c r="E95">
-        <v>-37.54651067571111</v>
+        <v>-42.21206385583066</v>
       </c>
       <c r="F95">
-        <v>-0.7692925287163667</v>
+        <v>-3.367158734923175</v>
       </c>
       <c r="G95">
-        <v>-7.252912746281859</v>
+        <v>-11.80227065768545</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.315856923557954</v>
       </c>
       <c r="E96">
-        <v>-40.42936666407511</v>
+        <v>-44.34575853944672</v>
       </c>
       <c r="F96">
-        <v>-1.053168239083938</v>
+        <v>-3.438073611542035</v>
       </c>
       <c r="G96">
-        <v>-6.831203589018905</v>
+        <v>-12.2960846587172</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.22264588662944</v>
       </c>
       <c r="E97">
-        <v>-42.1606068056815</v>
+        <v>-45.25905891307667</v>
       </c>
       <c r="F97">
-        <v>-1.319761720326903</v>
+        <v>-3.475485996922071</v>
       </c>
       <c r="G97">
-        <v>-7.26725824693975</v>
+        <v>-11.68765102617092</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.133885095836465</v>
       </c>
       <c r="E98">
-        <v>-44.332933901057</v>
+        <v>-47.29497025744512</v>
       </c>
       <c r="F98">
-        <v>-1.355309450683238</v>
+        <v>-3.696289813240488</v>
       </c>
       <c r="G98">
-        <v>-7.48448167661811</v>
+        <v>-12.38011018041146</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.056544904531609</v>
       </c>
       <c r="E99">
-        <v>-45.99869910122348</v>
+        <v>-48.12100240847325</v>
       </c>
       <c r="F99">
-        <v>-1.643342737045459</v>
+        <v>-4.142076559424445</v>
       </c>
       <c r="G99">
-        <v>-7.777527574092117</v>
+        <v>-12.96733727801904</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.991743737049094</v>
       </c>
       <c r="E100">
-        <v>-48.93111584124593</v>
+        <v>-49.85820428611073</v>
       </c>
       <c r="F100">
-        <v>-1.901478587105841</v>
+        <v>-4.17362079012305</v>
       </c>
       <c r="G100">
-        <v>-8.129225306941199</v>
+        <v>-12.94535309357076</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.928977485876895</v>
       </c>
       <c r="E101">
-        <v>-50.11924703816439</v>
+        <v>-52.46408069026958</v>
       </c>
       <c r="F101">
-        <v>-1.927300455785907</v>
+        <v>-4.156037035263825</v>
       </c>
       <c r="G101">
-        <v>-8.430260978912454</v>
+        <v>-12.84680816647596</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.883797413340714</v>
       </c>
       <c r="E102">
-        <v>-52.94587975748616</v>
+        <v>-52.94048974129853</v>
       </c>
       <c r="F102">
-        <v>-2.206639197888346</v>
+        <v>-4.455435522392456</v>
       </c>
       <c r="G102">
-        <v>-8.533389772525801</v>
+        <v>-12.92684044153237</v>
       </c>
     </row>
   </sheetData>
